--- a/data/gpt_examples/action/passes.xlsx
+++ b/data/gpt_examples/action/passes.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10208"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nikitha\shotsGPT\data\gpt_examples\action\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pegra441/Desktop/passesGPT-1/data/gpt_examples/action/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50EC62A-3ED0-DC45-BE06-81CACB72C8FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4545"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23600" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="passes" sheetId="1" r:id="rId1"/>
@@ -27,40 +28,42 @@
     <t>assistant</t>
   </si>
   <si>
-    <t>The pass is a forward pass originated from the attacking zone and the passer is rasmus orqvist from Degerfors team. The xT value is 0.23286607155768857 and it did not lead to a shot, opportunities to score goal is less and was a safe pass. It was a long pass with narrow angle covering distance 33.55m aiming towards the goal area, a bold attacking move. There were 1 teammates positioned ahead of the passer at the moment of the pass. There were 4 opponents positioned ahead of the passer at the moment of the pass. The passing lane was mostly open with few opponents and there were 2 opponents bypassed within 5m. There are no nearby opponents within 6m, creating low pressure at the moment of the pass.
-The contributions of the features to the xT, sorted by their magnitude from largest to smallest, are as follows:
-The most impactful feature is end distance to goal, which had the maximum positive contribution because the pass ended from a moderate distance to the goal. This feature increased the xT. Another impactful feature is opponents beyond, which had the maximum positive contribution because few opponents were ahead of the passer. This feature increased the xT. Another impactful feature is start distance to goal, which had the maximum positive contribution because the pass started far from the goal. This feature increased the xT. Another impactful feature is teammates beyond, which had the maximum positive contribution because there were few teammates ahead of passer. This feature increased the xT. Another impactful feature is start distance to sideline, which had the maximum negative contribution because the pass started close to the sideline. This feature reduced the xT.</t>
-  </si>
-  <si>
-    <t>What a bold pass from Rasmus Örqvist! Launching a long, daring ball (0.23 xT) from the attacking zone towards the heart of the goal area. With only low pressure around him and a mostly open passing lane, Örqvist seized the moment, threading a precise pass that bypassed two opponents within close range. Despite facing four defenders ahead, his vision and courage shone through, creating a valuable attacking move for Degerfors. A brave attempt that, while it didn’t lead directly to a shot, opened up promising space and pushed the momentum firmly in Degerfors' favor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The pass is a forward pass originated from the attacking zone and the passer is arian kabashi from Helsingborg team. It had high xT 0.12507612553155467 value and probability of pass being a shot was 13% with xG value 0.001. There is high chances of being a safe pass creating less goal scoring opportunities. It was a short pass with wide-angle covering distance 34.49m aiming to the goal area, possibly trying to spread out the defense and create space. There were 3 teammates positioned ahead of the passer at the moment of the pass. There were 6 opponents positioned ahead of the passer at the moment of the pass. The passing lane was crowded with opponents and there was 1 opponent bypassed within 5m. There are 2 nearby opponents within 6m, creating low pressure at the moment of the pass. The contributions of the features to the xT, sorted by their magnitude from largest to smallest, are as follows: The most impactful feature is start distance to sideline, which had the maximum positive contribution because the pass started close to the center of the pitch. This feature increased the xT. Another impactful feature is start distance to goal, which had the maximum positive contribution because the pass started far from the goal. This feature increased the xT. Another impactful feature is end distance to sideline, which had the maximum negative contribution because the pass ended at exact center line of the pitch. This feature reduced the xT. Another impactful feature is end distance to goal, which had the maximum positive contribution because the pass ended from a moderate distance to the goal. This feature increased the xT. Another impactful feature is pass angle, which had the maximum negative contribution because the pass angle was extremely forward, potentially a long ball or through ball. This feature reduced the xT. Another impactful feature is opponents beyond, which had the maximum positive contribution because a moderate number of opponents were ahead of the passer. This feature increased the xT. </t>
-  </si>
-  <si>
-    <t>A clever move from Arian Kabashi! Spotting a tight window amidst a crowded defense, he delivered a sharp, short pass (0.13 xT) aimed towards the goal area. Despite six opponents positioned ahead and a busy passing lane, Kabashi showed composure under low pressure, slipping the ball past a nearby defender. With a 13% chance of it becoming a shot, his decision prioritized safety while still stretching the opposition’s structure. A smart and tactical play, designed not to force a risky finish, but to shift the balance and carve out space for Helsingborg's next attack.</t>
-  </si>
-  <si>
-    <t>The pass is a forward pass originated from the middle zone and the passer is amar muhsin from Helsingborg team. It had excellent xT 0.19928129682688014 value and probability of pass being a shot was 20% creating a excellent goal scoring opportunities for safe pass. It was a long pass with wide-angle covering distance 42.58m aiming to the goal area, possibly trying to spread out the defense and create space. There were 2 teammates positioned ahead of the passer at the moment of the pass. There were 5 opponents positioned ahead of the passer at the moment of the pass. The passing lane was crowded with opponents and there were 2 opponents bypassed within 5m. There are 4 nearby opponents within 6m, creating moderate pressure at the moment of the pass.
-The contributions of the features to the xT, sorted by their magnitude from largest to smallest, are as follows:
-The most impactful feature is end distance to goal, which had the maximum positive contribution because the pass ended from a moderate distance to the goal. This feature increased the xT. Another impactful feature is opponents nearby, which had the maximum negative contribution because there were more number of opponents nearby passer at the moment of the pass. This feature reduced the xT. Another impactful feature is opponents beyond, which had the maximum positive contribution because few opponents were ahead of the passer. This feature increased the xT. Another impactful feature is teammates beyond, which had the maximum positive contribution because there were few teammates ahead of passer. This feature increased the xT. Another impactful feature is start distance to sideline, which had the maximum positive contribution because the pass started near the central area of the pitch. This feature increased the xT. Another impactful feature is pass angle, which had the maximum positive contribution because the pass angle was extremely forward, potentially a long ball or through ball. This feature increased the xT.</t>
-  </si>
-  <si>
-    <t>What an exceptional vision from Amar Muhsin! From the middle zone, he unleashed a brilliant long pass (0.20 xT) covering over 42 meters, aiming to pierce the defense wide open. Under moderate pressure with four opponents closing in, Muhsin kept his composure, threading a forward-angled ball through a crowded lane, bypassing two defenders in close proximity. Despite the congestion, his pass created a 20% chance of leading directly to a shot, offering Helsingborg an excellent attacking opportunity. His choice to launch from a central area and target a moderate distance to the goal maximized the threat — a bold and intelligent play that pushed the momentum sharply in Helsingborg’s favor.</t>
-  </si>
-  <si>
-    <t>The pass is a lateral pass originated from the attacking zone and the passer is elyas bouzaiene from Degerfors team. It had excellent xT 0.23551693990059663 value and probability of pass being a shot was 24% creating a excellent goal scoring opportunities for dangerous pass. It was a long pass with narrow angle covering distance 27.35m aiming towards the goal area, a bold attacking move. There were 1 teammates positioned ahead of the passer at the moment of the pass. There were 5 opponents positioned ahead of the passer at the moment of the pass. The passing lane was crowded with opponents and there were 2 opponents bypassed within 5m. There is 1 nearby opponent within 6m, creating low pressure at the moment of the pass.
-The contributions of the features to the xT, sorted by their magnitude from largest to smallest, are as follows:
-The most impactful feature is end distance to goal, which had the maximum positive contribution because the pass ended from a moderate distance to the goal. This feature increased the xT. Another impactful feature is start distance to goal, which had the maximum positive contribution because the pass started from a moderate distance to the goal. This feature increased the xT. Another impactful feature is teammates beyond, which had the maximum positive contribution because there were few teammates ahead of passer. This feature increased the xT. Another impactful feature is end distance to sideline, which had the maximum negative contribution because the pass ended at exact center line of the pitch. This feature reduced the xT. Another impactful feature is opponents beyond, which had the maximum positive contribution because few opponents were ahead of the passer. This feature increased the xT.</t>
-  </si>
-  <si>
-    <t>A daring play from Elyas Bouzaiene! From the attacking zone, he delivered a bold lateral pass (0.24 xT) slicing across 27 meters toward the goal area. Despite a crowded passing lane and five opponents ahead, Bouzaiene found a way to bypass two defenders under low pressure, carving open an excellent scoring opportunity for Degerfors. With a 24% chance of leading to a shot, this dangerous long ball showcased his attacking intent and vision. Launching from a moderate distance and targeting the heart of the pitch, Bouzaiene’s precision and risk-taking helped drive Degerfors into a prime position to strike.</t>
+    <t>sebastian ohlsson of Degerfors played a forward pass from the central zone into the wing. Despite an xT of 0.06, which indicates a moderate probability of ending in a quality shot, this pass didn’t lead to an attempt on goal. It was a long pass with a wide angle, covering around 57 metres and moving the ball toward the goal area. There were 8 teammates positioned ahead of the passer at the moment of the pass. There were 11 opponents positioned ahead of the passer at the moment of the pass. The passing lane was crowded with opponents. Two opponents were bypassed within 5 metres of the ball. There were no nearby opponents within 6 metres of the passer, meaning the pressure was low at the moment of the pass.
+Below is an analysis of the most influential features behind this pass’s xT value:
+The distance of the pass to the sideline after the pass was made had the strongest impact: the pass ended close to the sideline. It reduced the danger of the pass. The distance of the passer to the sideline at the start of the pass also stood out: the pass started close to the center of the pitch. It boosted the threat level of the pass. The number of opponents positioned ahead of the passer also stood out: many opponents were ahead of the passer. It reduced the danger of the pass. The distance from the passer to the opponent's goal at the start of the pass also stood out: the pass started far from the goal. It reduced the danger of the pass. The number of teammates positioned ahead of the passer also stood out: there were many teammates ahead of passer. It reduced the danger of the pass. The number of opponents close to the passer also stood out: there were no opponents nearby passer at the moment of the pass. It boosted the threat level of the pass. The angle from the passer to the goal also stood out: the pass started from a wide angle to the goal. It boosted the threat level of the pass. The direction of the pass relative to the goal also stood out: the pass angle was extremely forward, potentially a long ball or through ball. It boosted the threat level of the pass.</t>
+  </si>
+  <si>
+    <t>Sebastian Ohlsson of Degerfors, operating from a central zone under no immediate pressure, launched a formidable 57-meter forward pass with a wide angle, driving the ball towards the wing and bypassing two opponents despite a crowded lane. Although his central starting position, an open angle to goal, and the aggressive forward direction increased its potential, the pass's moderate 0.06 xT was ultimately curbed by its destination close to the sideline and the sheer number of defenders positioned ahead, preventing a shot on goal.</t>
+  </si>
+  <si>
+    <t>gustaf lagerbielke of Degerfors played a forward pass from the central zone into the ft half-space. Despite an xT of 0.14, which indicates a excellent probability of ending in a quality shot, this pass didn’t lead to an attempt on goal. It was a long pass with a wide angle, covering around 57 metres and moving the ball toward the goal area. There were 9 teammates positioned ahead of the passer at the moment of the pass. There were 11 opponents positioned ahead of the passer at the moment of the pass. The passing lane was crowded with opponents. Two opponents were bypassed within 5 metres of the ball. There were no nearby opponents within 6 metres of the passer, meaning the pressure was low at the moment of the pass.
+Below is an analysis of the most influential features behind this pass’s xT value:
+The angle from the receiver to the goal had the strongest impact: the pass ended from a moderate angle to the goal. It boosted the threat level of the pass. The distance of the passer to the sideline at the start of the pass also stood out: the pass started close to the center of the pitch. It boosted the threat level of the pass. The number of opponents positioned ahead of the passer also stood out: many opponents were ahead of the passer. It reduced the danger of the pass. The distance from the passer to the opponent's goal at the start of the pass also stood out: the pass started far from the goal. It reduced the danger of the pass. The number of teammates positioned ahead of the passer also stood out: there were many teammates ahead of passer. It reduced the danger of the pass. The distance of the pass to the sideline after the pass was made also stood out: the pass ended close to the center of the pitch. It boosted the threat level of the pass. The length of the pass also stood out: the pass was long. It reduced the danger of the pass. The direction of the pass relative to the goal also stood out: the pass angle was extremely forward, potentially a long ball or through ball. It boosted the threat level of the pass. The number of opponents close to the passer also stood out: there were no opponents nearby passer at the moment of the pass. It boosted the threat level of the pass. The angle from the passer to the goal also stood out: the pass started from a wide angle to the goal. It boosted the threat level of the pass. The distance from the receiver to the opponent's goal when the pass arrived also stood out: the pass ended from a moderate distance to the goal. It reduced the danger of the pass.</t>
+  </si>
+  <si>
+    <t>Gustaf Lagerbielke, operating from the central zone, launched a brilliant, long forward pass (0.14 xT) that covered approximately 57 meters, piercing into the dangerous front half-space towards the goal area. With no immediate pressure on him, he impressively threaded the ball through a crowded lane, bypassing two opponents with his ambitious delivery. Despite the excellent forward angle of the pass and its central origin boosting the threat, the sheer number of opponents ahead and the overall length of the pass meant it ultimately didn't translate into an immediate shot on goal.</t>
+  </si>
+  <si>
+    <t>elyas bouzaiene of Degerfors played a back pass from the ft half-space into the wing. Despite an xT of 0.13, which indicates a high probability of ending in a quality shot, this pass didn’t lead to an attempt on goal. It was a short pass with a narrow angle, covering around 17 metres and moving the ball toward the goal area. There were 10 teammates positioned ahead of the passer at the moment of the pass. There were 10 opponents positioned ahead of the passer at the moment of the pass. The passing lane was mostly open, with only a few opponents in the way. No opponents were bypassed within 5 metres of the ball. There was one nearby opponent within 6 metres of the passer, but overall the pressure was still low.
+Below is an analysis of the most influential features behind this pass’s xT value:
+The angle from the receiver to the goal had the strongest impact: the pass ended from a narrow angle to the goal. It boosted the threat level of the pass. The distance from the passer to the opponent's goal at the start of the pass also stood out: the pass started from a moderate distance to the goal. It boosted the threat level of the pass. The distance of the pass to the sideline after the pass was made also stood out: the pass started moderately close to the sideline. It reduced the danger of the pass. The number of teammates positioned ahead of the passer also stood out: there were many teammates ahead of passer. It reduced the danger of the pass. The number of opponents positioned ahead of the passer also stood out: many opponents were ahead of the passer. It reduced the danger of the pass.</t>
+  </si>
+  <si>
+    <t>Elyas Bouzaiene of Degerfors played a precise short back pass (0.13 xT) from the half-space to the wing, moving the ball towards the goal area under low pressure with a mostly open passing lane, though without bypassing any immediate opponents. Its strong threat level was boosted by the moderate starting distance from goal and the narrow angle the receiver had to goal, but the danger was slightly reduced by the ball ending moderately close to the sideline and the high number of players positioned further upfield.</t>
+  </si>
+  <si>
+    <t>diego ballestero of Degerfors played a lateral pass from the central zone into the ft half-space. Despite an xT of 0.16, which indicates a excellent probability of ending in a quality shot, this pass didn’t lead to an attempt on goal. It was a short pass with a moderate angle, covering around 25 metres toward the goal area. There were 3 teammates positioned ahead of the passer at the moment of the pass. There were 8 opponents positioned ahead of the passer at the moment of the pass. The passing lane was crowded with opponents. Three opponents were bypassed within 5 metres of the ball. There were 2 nearby opponents within 6 metres of the passer, but the situation was still classified as low pressure.
+Below is an analysis of the most influential features behind this pass’s xT value:
+The distance from the passer to the opponent's goal at the start of the pass had the strongest impact: the pass started from a moderate distance to the goal. It boosted the threat level of the pass. The distance of the passer to the sideline at the start of the pass also stood out: the pass started close to the center of the pitch. It boosted the threat level of the pass. The distance of the pass to the sideline after the pass was made also stood out: the pass ended close to the center of the pitch. It boosted the threat level of the pass. The number of teammates positioned ahead of the passer also stood out: there were few teammates ahead of passer. It boosted the threat level of the pass.</t>
+  </si>
+  <si>
+    <t>From the central zone, Diego Ballestero of Degerfors played a sharp lateral pass covering 25 meters towards the goal area, adeptly bypassing three opponents through a crowded lane while operating under low pressure. Despite not leading to a shot, this pass carried an excellent 0.16 xT threat, significantly boosted by its advantageous central starting and ending positions, and its moderate distance from goal, which created dangerous opportunities even with fewer teammates ahead.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -357,7 +360,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -366,7 +369,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="11"/>
       <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -647,15 +650,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" customWidth="1"/>
-    <col min="2" max="2" width="73.140625" customWidth="1"/>
+    <col min="1" max="1" width="67" customWidth="1"/>
+    <col min="2" max="2" width="73.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,7 +666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -671,7 +674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="408.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="409" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -679,7 +682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="350" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -687,7 +690,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -695,7 +698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
     </row>
   </sheetData>

--- a/data/gpt_examples/action/passes.xlsx
+++ b/data/gpt_examples/action/passes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10215"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pegra441/Desktop/passesGPT-1/data/gpt_examples/action/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50EC62A-3ED0-DC45-BE06-81CACB72C8FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430B65D1-0B41-D349-AC58-2DBBE589B3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23600" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="23600" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="passes" sheetId="1" r:id="rId1"/>
@@ -33,31 +33,31 @@
 The distance of the pass to the sideline after the pass was made had the strongest impact: the pass ended close to the sideline. It reduced the danger of the pass. The distance of the passer to the sideline at the start of the pass also stood out: the pass started close to the center of the pitch. It boosted the threat level of the pass. The number of opponents positioned ahead of the passer also stood out: many opponents were ahead of the passer. It reduced the danger of the pass. The distance from the passer to the opponent's goal at the start of the pass also stood out: the pass started far from the goal. It reduced the danger of the pass. The number of teammates positioned ahead of the passer also stood out: there were many teammates ahead of passer. It reduced the danger of the pass. The number of opponents close to the passer also stood out: there were no opponents nearby passer at the moment of the pass. It boosted the threat level of the pass. The angle from the passer to the goal also stood out: the pass started from a wide angle to the goal. It boosted the threat level of the pass. The direction of the pass relative to the goal also stood out: the pass angle was extremely forward, potentially a long ball or through ball. It boosted the threat level of the pass.</t>
   </si>
   <si>
-    <t>Sebastian Ohlsson of Degerfors, operating from a central zone under no immediate pressure, launched a formidable 57-meter forward pass with a wide angle, driving the ball towards the wing and bypassing two opponents despite a crowded lane. Although his central starting position, an open angle to goal, and the aggressive forward direction increased its potential, the pass's moderate 0.06 xT was ultimately curbed by its destination close to the sideline and the sheer number of defenders positioned ahead, preventing a shot on goal.</t>
-  </si>
-  <si>
     <t>gustaf lagerbielke of Degerfors played a forward pass from the central zone into the ft half-space. Despite an xT of 0.14, which indicates a excellent probability of ending in a quality shot, this pass didn’t lead to an attempt on goal. It was a long pass with a wide angle, covering around 57 metres and moving the ball toward the goal area. There were 9 teammates positioned ahead of the passer at the moment of the pass. There were 11 opponents positioned ahead of the passer at the moment of the pass. The passing lane was crowded with opponents. Two opponents were bypassed within 5 metres of the ball. There were no nearby opponents within 6 metres of the passer, meaning the pressure was low at the moment of the pass.
 Below is an analysis of the most influential features behind this pass’s xT value:
 The angle from the receiver to the goal had the strongest impact: the pass ended from a moderate angle to the goal. It boosted the threat level of the pass. The distance of the passer to the sideline at the start of the pass also stood out: the pass started close to the center of the pitch. It boosted the threat level of the pass. The number of opponents positioned ahead of the passer also stood out: many opponents were ahead of the passer. It reduced the danger of the pass. The distance from the passer to the opponent's goal at the start of the pass also stood out: the pass started far from the goal. It reduced the danger of the pass. The number of teammates positioned ahead of the passer also stood out: there were many teammates ahead of passer. It reduced the danger of the pass. The distance of the pass to the sideline after the pass was made also stood out: the pass ended close to the center of the pitch. It boosted the threat level of the pass. The length of the pass also stood out: the pass was long. It reduced the danger of the pass. The direction of the pass relative to the goal also stood out: the pass angle was extremely forward, potentially a long ball or through ball. It boosted the threat level of the pass. The number of opponents close to the passer also stood out: there were no opponents nearby passer at the moment of the pass. It boosted the threat level of the pass. The angle from the passer to the goal also stood out: the pass started from a wide angle to the goal. It boosted the threat level of the pass. The distance from the receiver to the opponent's goal when the pass arrived also stood out: the pass ended from a moderate distance to the goal. It reduced the danger of the pass.</t>
   </si>
   <si>
-    <t>Gustaf Lagerbielke, operating from the central zone, launched a brilliant, long forward pass (0.14 xT) that covered approximately 57 meters, piercing into the dangerous front half-space towards the goal area. With no immediate pressure on him, he impressively threaded the ball through a crowded lane, bypassing two opponents with his ambitious delivery. Despite the excellent forward angle of the pass and its central origin boosting the threat, the sheer number of opponents ahead and the overall length of the pass meant it ultimately didn't translate into an immediate shot on goal.</t>
-  </si>
-  <si>
     <t>elyas bouzaiene of Degerfors played a back pass from the ft half-space into the wing. Despite an xT of 0.13, which indicates a high probability of ending in a quality shot, this pass didn’t lead to an attempt on goal. It was a short pass with a narrow angle, covering around 17 metres and moving the ball toward the goal area. There were 10 teammates positioned ahead of the passer at the moment of the pass. There were 10 opponents positioned ahead of the passer at the moment of the pass. The passing lane was mostly open, with only a few opponents in the way. No opponents were bypassed within 5 metres of the ball. There was one nearby opponent within 6 metres of the passer, but overall the pressure was still low.
 Below is an analysis of the most influential features behind this pass’s xT value:
 The angle from the receiver to the goal had the strongest impact: the pass ended from a narrow angle to the goal. It boosted the threat level of the pass. The distance from the passer to the opponent's goal at the start of the pass also stood out: the pass started from a moderate distance to the goal. It boosted the threat level of the pass. The distance of the pass to the sideline after the pass was made also stood out: the pass started moderately close to the sideline. It reduced the danger of the pass. The number of teammates positioned ahead of the passer also stood out: there were many teammates ahead of passer. It reduced the danger of the pass. The number of opponents positioned ahead of the passer also stood out: many opponents were ahead of the passer. It reduced the danger of the pass.</t>
   </si>
   <si>
-    <t>Elyas Bouzaiene of Degerfors played a precise short back pass (0.13 xT) from the half-space to the wing, moving the ball towards the goal area under low pressure with a mostly open passing lane, though without bypassing any immediate opponents. Its strong threat level was boosted by the moderate starting distance from goal and the narrow angle the receiver had to goal, but the danger was slightly reduced by the ball ending moderately close to the sideline and the high number of players positioned further upfield.</t>
-  </si>
-  <si>
     <t>diego ballestero of Degerfors played a lateral pass from the central zone into the ft half-space. Despite an xT of 0.16, which indicates a excellent probability of ending in a quality shot, this pass didn’t lead to an attempt on goal. It was a short pass with a moderate angle, covering around 25 metres toward the goal area. There were 3 teammates positioned ahead of the passer at the moment of the pass. There were 8 opponents positioned ahead of the passer at the moment of the pass. The passing lane was crowded with opponents. Three opponents were bypassed within 5 metres of the ball. There were 2 nearby opponents within 6 metres of the passer, but the situation was still classified as low pressure.
 Below is an analysis of the most influential features behind this pass’s xT value:
 The distance from the passer to the opponent's goal at the start of the pass had the strongest impact: the pass started from a moderate distance to the goal. It boosted the threat level of the pass. The distance of the passer to the sideline at the start of the pass also stood out: the pass started close to the center of the pitch. It boosted the threat level of the pass. The distance of the pass to the sideline after the pass was made also stood out: the pass ended close to the center of the pitch. It boosted the threat level of the pass. The number of teammates positioned ahead of the passer also stood out: there were few teammates ahead of passer. It boosted the threat level of the pass.</t>
   </si>
   <si>
-    <t>From the central zone, Diego Ballestero of Degerfors played a sharp lateral pass covering 25 meters towards the goal area, adeptly bypassing three opponents through a crowded lane while operating under low pressure. Despite not leading to a shot, this pass carried an excellent 0.16 xT threat, significantly boosted by its advantageous central starting and ending positions, and its moderate distance from goal, which created dangerous opportunities even with fewer teammates ahead.</t>
+    <t>Sebastian Ohlsson fired a 57 m forward pass to the wing, bypassing two opponents but creating only 0.06 xT. Its threat was mainly limited because the ball ended near the sideline.</t>
+  </si>
+  <si>
+    <t>Gustaf Lagerbielke played a 57 m forward pass from the central zone into the front half-space, creating 0.14 xT but no shot. The main factor increasing its threat was the central starting position and strong forward angle toward goal.</t>
+  </si>
+  <si>
+    <t>Elyas Bouzaiene played a short back pass from the half-space to the wing, generating 0.13 xT without leading to a shot. Its threat mainly came from the relatively close starting distance to goal.</t>
+  </si>
+  <si>
+    <t>Diego Ballestero played a 25 m lateral pass from the central zone, bypassing three opponents and generating 0.16 xT without a shot. Its threat mainly came from the central start and end positions close to goal.</t>
   </si>
 </sst>
 </file>
@@ -671,28 +671,28 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="409" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="350" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
